--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484309_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484309_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5801</v>
+        <v>7.9644</v>
       </c>
       <c r="E2" t="n">
-        <v>10.2466</v>
+        <v>9.8215</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6665</v>
+        <v>-1.8571</v>
       </c>
       <c r="G2" t="n">
         <v>2.6883</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0917</v>
+        <v>0.4759</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7705</v>
+        <v>0.3454</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3212</v>
+        <v>0.1305</v>
       </c>
       <c r="V2" t="n">
         <v>3.8234</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9132</v>
+        <v>7.188</v>
       </c>
       <c r="E3" t="n">
-        <v>10.3607</v>
+        <v>10.7445</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.4475</v>
+        <v>-3.5565</v>
       </c>
       <c r="G3" t="n">
         <v>6.2131</v>
@@ -688,13 +688,13 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1745</v>
+        <v>0.1004</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4566</v>
+        <v>-0.0728</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2822</v>
+        <v>0.1732</v>
       </c>
       <c r="V3" t="n">
         <v>2.4373</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5621</v>
+        <v>3.7099</v>
       </c>
       <c r="E4" t="n">
-        <v>1.711</v>
+        <v>1.9132</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8511</v>
+        <v>1.7966</v>
       </c>
       <c r="G4" t="n">
         <v>2.6784</v>
@@ -766,13 +766,13 @@
         <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1711</v>
+        <v>-0.0234</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6052</v>
+        <v>-0.403</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4341</v>
+        <v>0.3796</v>
       </c>
       <c r="V4" t="n">
         <v>0.6642</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0203</v>
+        <v>2.7714</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4028</v>
+        <v>2.0995</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6175</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>2.0422</v>
@@ -844,13 +844,13 @@
         <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0572</v>
+        <v>-0.3061</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0083</v>
+        <v>-0.295</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0655</v>
+        <v>-0.0111</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3321</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4002</v>
+        <v>0.6841</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2327</v>
+        <v>2.4349</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8325</v>
+        <v>-1.7508</v>
       </c>
       <c r="G6" t="n">
         <v>3.199</v>
@@ -922,13 +922,13 @@
         <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6388</v>
+        <v>-0.3549</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5915</v>
+        <v>-0.3892</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0474</v>
+        <v>0.0343</v>
       </c>
       <c r="V6" t="n">
         <v>-2.16</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1105</v>
+        <v>0.2389</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0413</v>
+        <v>0.1425</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0692</v>
+        <v>0.0964</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2378</v>
@@ -1000,13 +1000,13 @@
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0424</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0605</v>
+        <v>0.0406</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6593</v>
+        <v>-1.1389</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7261</v>
+        <v>2.301</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3854</v>
+        <v>-3.4399</v>
       </c>
       <c r="G8" t="n">
         <v>-4.3772</v>
@@ -1078,13 +1078,13 @@
         <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6007</v>
+        <v>1.1211</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3236</v>
+        <v>0.8985</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2771</v>
+        <v>0.2227</v>
       </c>
       <c r="V8" t="n">
         <v>0.5545</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5381</v>
+        <v>-1.7208</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3205</v>
+        <v>0.3062</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2177</v>
+        <v>-2.027</v>
       </c>
       <c r="G9" t="n">
         <v>-2.679</v>
@@ -1156,13 +1156,13 @@
         <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8358</v>
+        <v>-0.0186</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4842</v>
+        <v>0.1424</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3517</v>
+        <v>-0.161</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8038</v>
+        <v>-3.5776</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3467</v>
+        <v>-0.6733</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.457</v>
+        <v>-2.9043</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4249</v>
+        <v>-4.4148</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3443</v>
+        <v>-0.638</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0805</v>
+        <v>-3.7767</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4301</v>
+        <v>-1.0877</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3492</v>
+        <v>-0.5488</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>-0.5389</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0052</v>
+        <v>-3.3271</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0049</v>
+        <v>-0.0893</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0004</v>
+        <v>-3.2379</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0914</v>
+        <v>0.0213</v>
       </c>
       <c r="T10" t="n">
-        <v>0.864</v>
+        <v>0.2979</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7726</v>
+        <v>-0.2766</v>
       </c>
       <c r="V10" t="n">
-        <v>-4.3201</v>
+        <v>2.7693</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>3.0466</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.6559</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6576</v>
+        <v>-4.4571</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5627</v>
+        <v>-1.0545</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0949</v>
+        <v>-3.4026</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.4148</v>
+        <v>0.4249</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.638</v>
+        <v>0.3443</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.7767</v>
+        <v>0.0805</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0877</v>
+        <v>0.4301</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5488</v>
+        <v>0.3492</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5389</v>
+        <v>0.0809</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3271</v>
+        <v>-0.0052</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0893</v>
+        <v>-0.0049</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.2379</v>
+        <v>-0.0004</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0587</v>
+        <v>-0.5619</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5915</v>
+        <v>0.1562</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4673</v>
+        <v>-0.7181</v>
       </c>
       <c r="V11" t="n">
-        <v>2.7693</v>
+        <v>-4.3201</v>
       </c>
       <c r="W11" t="n">
-        <v>3.0466</v>
+        <v>-0.6642</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2772</v>
+        <v>-3.6559</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.7321</v>
+        <v>-7.5589</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.8191</v>
+        <v>-6.4552</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.913</v>
+        <v>-1.1037</v>
       </c>
       <c r="G12" t="n">
         <v>-6.1201</v>
@@ -1390,13 +1390,13 @@
         <v>1.7581</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1079</v>
+        <v>0.0653</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0246</v>
+        <v>0.3392</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0833</v>
+        <v>-0.2739</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3321</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.195499999999996</v>
+        <v>4.103400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>20.67220000000001</v>
+        <v>21.5803</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.4767</v>
+        <v>-17.477</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5830000000000028</v>
+        <v>-0.583000000000002</v>
       </c>
       <c r="H13" t="n">
         <v>8.860300000000001</v>
@@ -1468,10 +1468,10 @@
         <v>14.6506</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3026000000000001</v>
+        <v>0.6051000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1523</v>
+        <v>1.0602</v>
       </c>
       <c r="U13" t="n">
         <v>-0.455</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3177</v>
+        <v>5.8362</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1228</v>
+        <v>6.4262</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8051</v>
+        <v>-0.59</v>
       </c>
       <c r="G14" t="n">
         <v>5.3431</v>
@@ -1546,13 +1546,13 @@
         <v>0.586</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8315</v>
+        <v>-0.3129</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2888</v>
+        <v>0.0145</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5426</v>
+        <v>-0.3275</v>
       </c>
       <c r="V14" t="n">
         <v>1.1967</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.564</v>
+        <v>3.1176</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3735</v>
+        <v>3.5758</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8095</v>
+        <v>-0.4582</v>
       </c>
       <c r="G15" t="n">
         <v>1.1087</v>
@@ -1624,13 +1624,13 @@
         <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1133</v>
+        <v>0.4403</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2175</v>
+        <v>0.4197</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3308</v>
+        <v>0.0206</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1895</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1756</v>
+        <v>1.4256</v>
       </c>
       <c r="E16" t="n">
-        <v>4.505</v>
+        <v>3.1392</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3294</v>
+        <v>-1.7137</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5876</v>
+        <v>2.6425</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3963</v>
+        <v>-1.7012</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8087</v>
+        <v>4.3437</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5999</v>
+        <v>5.993</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4234</v>
+        <v>0.165</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0233</v>
+        <v>5.8281</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1874</v>
+        <v>-3.3506</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9729</v>
+        <v>-1.8662</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2146</v>
+        <v>-1.4844</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7399</v>
+        <v>0.1176</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4446</v>
+        <v>-0.1656</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2953</v>
+        <v>0.2832</v>
       </c>
       <c r="V16" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.2186</v>
       </c>
-      <c r="W16" t="n">
-        <v>2.4373</v>
-      </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2182</v>
+        <v>1.1008</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0381</v>
+        <v>3.595</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8199</v>
+        <v>-2.4942</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6425</v>
+        <v>-0.5876</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7012</v>
+        <v>-1.3963</v>
       </c>
       <c r="I17" t="n">
-        <v>4.3437</v>
+        <v>0.8087</v>
       </c>
       <c r="J17" t="n">
-        <v>5.993</v>
+        <v>1.5999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.165</v>
+        <v>-0.4234</v>
       </c>
       <c r="L17" t="n">
-        <v>5.8281</v>
+        <v>2.0233</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.3506</v>
+        <v>-2.1874</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8662</v>
+        <v>-0.9729</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4844</v>
+        <v>-1.2146</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0897</v>
+        <v>0.6651</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2667</v>
+        <v>0.5346</v>
       </c>
       <c r="U17" t="n">
-        <v>0.177</v>
+        <v>0.1305</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0329</v>
+        <v>1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>2.4373</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1857</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1345</v>
+        <v>-1.1189</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5143</v>
+        <v>0.312</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6488</v>
+        <v>-1.4309</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6159</v>
@@ -1858,13 +1858,13 @@
         <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1261</v>
+        <v>0.1417</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2504</v>
+        <v>0.0482</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1244</v>
+        <v>0.0935</v>
       </c>
       <c r="V18" t="n">
         <v>0.9414</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4574</v>
+        <v>-1.4302</v>
       </c>
       <c r="E19" t="n">
         <v>-1.615</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1576</v>
+        <v>0.1848</v>
       </c>
       <c r="G19" t="n">
         <v>-1.294</v>
@@ -1936,13 +1936,13 @@
         <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1634</v>
+        <v>-0.1362</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1678</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0044</v>
+        <v>0.0316</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5774</v>
+        <v>-1.6628</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2592</v>
+        <v>0.9559</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8366</v>
+        <v>-2.6187</v>
       </c>
       <c r="G20" t="n">
         <v>0.6871</v>
@@ -2014,13 +2014,13 @@
         <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5635</v>
+        <v>0.478</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3385</v>
+        <v>0.0352</v>
       </c>
       <c r="U20" t="n">
-        <v>0.225</v>
+        <v>0.4429</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4373</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9181</v>
+        <v>-2.1762</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3163</v>
+        <v>0.114</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2344</v>
+        <v>-2.2902</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4417</v>
@@ -2092,13 +2092,13 @@
         <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>0.701</v>
+        <v>0.443</v>
       </c>
       <c r="T21" t="n">
-        <v>0.278</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.423</v>
+        <v>0.3672</v>
       </c>
       <c r="V21" t="n">
         <v>-2.3495</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9863</v>
+        <v>-2.6548</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2927</v>
+        <v>1.0005</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.279</v>
+        <v>-3.6553</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8309</v>
@@ -2170,13 +2170,13 @@
         <v>1.9534</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.434</v>
+        <v>-0.1025</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8198</v>
+        <v>-0.112</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6142</v>
+        <v>0.0095</v>
       </c>
       <c r="V22" t="n">
         <v>0.2553</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3975</v>
+        <v>-4.2848</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3302</v>
+        <v>-0.0269</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.0673</v>
+        <v>-4.2579</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4284</v>
@@ -2248,13 +2248,13 @@
         <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.196</v>
+        <v>-0.0833</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5309</v>
+        <v>-0.2276</v>
       </c>
       <c r="U23" t="n">
-        <v>0.335</v>
+        <v>0.1443</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7731</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.195699999999999</v>
+        <v>-1.8475</v>
       </c>
       <c r="E24" t="n">
         <v>17.4767</v>
       </c>
       <c r="F24" t="n">
-        <v>-20.6724</v>
+        <v>-19.3243</v>
       </c>
       <c r="G24" t="n">
         <v>0.5828999999999986</v>
@@ -2326,13 +2326,13 @@
         <v>13.674</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3025999999999999</v>
+        <v>1.6508</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4550000000000003</v>
+        <v>0.455</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1522999999999999</v>
+        <v>1.1958</v>
       </c>
       <c r="V24" t="n">
         <v>-3.104499999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484309_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484309_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7714</v>
+        <v>1.8279</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0995</v>
+        <v>1.8279</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6719000000000001</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0422</v>
+        <v>1.8279</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2062</v>
+        <v>0.614</v>
       </c>
       <c r="I5" t="n">
-        <v>0.836</v>
+        <v>1.214</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7266</v>
+        <v>1.8279</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3507</v>
+        <v>0.614</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3758</v>
+        <v>1.214</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6844</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1445</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5399</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3061</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.295</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0111</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>M. SELLARES GIRALT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6841</v>
+        <v>1.5575</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4349</v>
+        <v>0.8855</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7508</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>3.199</v>
+        <v>0.8282</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1722</v>
+        <v>1.2062</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0268</v>
+        <v>-0.378</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2231</v>
+        <v>1.5126</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5214</v>
+        <v>1.3507</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7017</v>
+        <v>0.1619</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0241</v>
+        <v>-0.6844</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3492</v>
+        <v>-0.1445</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.5399</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3549</v>
+        <v>-0.3061</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3892</v>
+        <v>-0.295</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0343</v>
+        <v>-0.0111</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.16</v>
+        <v>-0.3321</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5545</v>
+        <v>-0.3321</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>M. SELLARÈS GIRALT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2389</v>
+        <v>1.214</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1425</v>
+        <v>1.214</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0964</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2378</v>
+        <v>1.214</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1433</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0946</v>
+        <v>1.214</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1019</v>
+        <v>1.214</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>1.214</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3397</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.135</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0406</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0454</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,12 +1046,17 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1389</v>
+        <v>0.2389</v>
       </c>
       <c r="E8" t="n">
-        <v>2.301</v>
+        <v>0.1425</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.4399</v>
+        <v>0.0964</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.3772</v>
+        <v>-0.2378</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.1433</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.8717</v>
+        <v>-0.0946</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3705</v>
+        <v>0.1019</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5462</v>
+        <v>0.0614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1757</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.0067</v>
+        <v>-0.3397</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0407</v>
+        <v>-0.2047</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.0474</v>
+        <v>-0.135</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1211</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8985</v>
+        <v>0.0406</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2227</v>
+        <v>0.0454</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7208</v>
+        <v>-1.1389</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3062</v>
+        <v>2.301</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.027</v>
+        <v>-3.4399</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.679</v>
+        <v>-4.3772</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0192</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6982</v>
+        <v>-3.8717</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1637</v>
+        <v>-0.3705</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1637</v>
+        <v>-0.5462</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.1757</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8427</v>
+        <v>-4.0067</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1445</v>
+        <v>0.0407</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.6982</v>
+        <v>-4.0474</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0186</v>
+        <v>1.1211</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1424</v>
+        <v>0.8985</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.161</v>
+        <v>0.2227</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5776</v>
+        <v>-1.1438</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6733</v>
+        <v>0.607</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9043</v>
+        <v>-1.7508</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.4148</v>
+        <v>1.3711</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.638</v>
+        <v>2.5582</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.7767</v>
+        <v>-1.1871</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0877</v>
+        <v>2.3952</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5488</v>
+        <v>2.9074</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5389</v>
+        <v>-0.5122</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.3271</v>
+        <v>-1.0241</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0893</v>
+        <v>-0.3492</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.2379</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.9534</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0213</v>
+        <v>-0.3549</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2979</v>
+        <v>-0.3892</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2766</v>
+        <v>0.0343</v>
       </c>
       <c r="V10" t="n">
-        <v>2.7693</v>
+        <v>-2.16</v>
       </c>
       <c r="W10" t="n">
-        <v>3.0466</v>
+        <v>0.5545</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4571</v>
+        <v>-1.7208</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0545</v>
+        <v>0.3062</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4026</v>
+        <v>-2.027</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4249</v>
+        <v>-2.679</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3443</v>
+        <v>0.0192</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0805</v>
+        <v>-2.6982</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4301</v>
+        <v>0.1637</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3492</v>
+        <v>0.1637</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0052</v>
+        <v>-2.8427</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0049</v>
+        <v>-0.1445</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0004</v>
+        <v>-2.6982</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5619</v>
+        <v>-0.0186</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1562</v>
+        <v>0.1424</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7181</v>
+        <v>-0.161</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.3201</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.6559</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.5589</v>
+        <v>-3.5776</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.4552</v>
+        <v>-0.6733</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1037</v>
+        <v>-2.9043</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.1201</v>
+        <v>-4.4148</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.3173</v>
+        <v>-0.638</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.8028</v>
+        <v>-3.7767</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.7509</v>
+        <v>-1.0877</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.8371</v>
+        <v>-0.5488</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9137</v>
+        <v>-0.5389</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3692</v>
+        <v>-3.3271</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5199</v>
+        <v>-0.0893</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8891</v>
+        <v>-3.2379</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0653</v>
+        <v>0.0213</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3392</v>
+        <v>0.2979</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2739</v>
+        <v>-0.2766</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3321</v>
+        <v>2.7693</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8865</v>
+        <v>3.0466</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,229 +1483,240 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.103400000000001</v>
+        <v>-4.4571</v>
       </c>
       <c r="E13" t="n">
-        <v>21.5803</v>
+        <v>-1.0545</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.477</v>
+        <v>-3.4026</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.583000000000002</v>
+        <v>0.4249</v>
       </c>
       <c r="H13" t="n">
-        <v>8.860300000000001</v>
+        <v>0.3443</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.4434</v>
+        <v>0.0805</v>
       </c>
       <c r="J13" t="n">
-        <v>21.1729</v>
+        <v>0.4301</v>
       </c>
       <c r="K13" t="n">
-        <v>11.0526</v>
+        <v>0.3492</v>
       </c>
       <c r="L13" t="n">
-        <v>10.1203</v>
+        <v>0.0809</v>
       </c>
       <c r="M13" t="n">
-        <v>-21.756</v>
+        <v>-0.0052</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.1923</v>
+        <v>-0.0049</v>
       </c>
       <c r="O13" t="n">
-        <v>-19.5639</v>
+        <v>-0.0004</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9766999999999997</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6738</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>14.6506</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6051000000000002</v>
+        <v>-0.5619</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0602</v>
+        <v>0.1562</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.455</v>
+        <v>-0.7181</v>
       </c>
       <c r="V13" t="n">
-        <v>3.104399999999999</v>
+        <v>-4.3201</v>
       </c>
       <c r="W13" t="n">
-        <v>13.0209</v>
+        <v>-0.6642</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.916500000000001</v>
+        <v>-3.6559</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8362</v>
+        <v>-7.5589</v>
       </c>
       <c r="E14" t="n">
-        <v>6.4262</v>
+        <v>-6.4552</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.59</v>
+        <v>-1.1037</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3431</v>
+        <v>-6.1201</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8378</v>
+        <v>-2.3173</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5053</v>
+        <v>-3.8028</v>
       </c>
       <c r="J14" t="n">
-        <v>5.8925</v>
+        <v>-4.7509</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9824000000000001</v>
+        <v>-2.8371</v>
       </c>
       <c r="L14" t="n">
-        <v>4.9102</v>
+        <v>-1.9137</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5494</v>
+        <v>-1.3692</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1445</v>
+        <v>0.5199</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4049</v>
+        <v>-1.8891</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3129</v>
+        <v>0.0653</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0145</v>
+        <v>0.3392</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3275</v>
+        <v>-0.2739</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1967</v>
+        <v>-0.3321</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4959</v>
+        <v>0.8865</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2992</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1176</v>
+        <v>4.103500000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5758</v>
+        <v>21.5803</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4582</v>
+        <v>-17.477</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1087</v>
+        <v>-0.583000000000002</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8066</v>
+        <v>8.860300000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9153</v>
+        <v>-9.443300000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1561</v>
+        <v>21.1729</v>
       </c>
       <c r="K15" t="n">
-        <v>0.431</v>
+        <v>11.0526</v>
       </c>
       <c r="L15" t="n">
-        <v>2.725</v>
+        <v>10.1205</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0474</v>
+        <v>-21.756</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2377</v>
+        <v>-2.1923</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8097</v>
+        <v>-19.5639</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7581</v>
+        <v>0.9766999999999997</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-13.6738</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>14.6506</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4403</v>
+        <v>0.6051000000000002</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4197</v>
+        <v>1.0602</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0206</v>
+        <v>-0.455</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1895</v>
+        <v>3.1044</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>13.0209</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1895</v>
-      </c>
+        <v>-9.916500000000001</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4256</v>
+        <v>5.8362</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1392</v>
+        <v>6.4262</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7137</v>
+        <v>-0.59</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6425</v>
+        <v>5.3431</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7012</v>
+        <v>0.8378</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3437</v>
+        <v>4.5053</v>
       </c>
       <c r="J16" t="n">
-        <v>5.993</v>
+        <v>5.8925</v>
       </c>
       <c r="K16" t="n">
-        <v>0.165</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>5.8281</v>
+        <v>4.9102</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.3506</v>
+        <v>-0.5494</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8662</v>
+        <v>-0.1445</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4844</v>
+        <v>-0.4049</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5395</v>
+        <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1176</v>
+        <v>-0.3129</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1656</v>
+        <v>0.0145</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2832</v>
+        <v>-0.3275</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0329</v>
+        <v>1.1967</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1857</v>
+        <v>-0.2992</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1008</v>
+        <v>3.1176</v>
       </c>
       <c r="E17" t="n">
-        <v>3.595</v>
+        <v>3.5758</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4942</v>
+        <v>-0.4582</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5876</v>
+        <v>1.1087</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3963</v>
+        <v>-0.8066</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8087</v>
+        <v>1.9153</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5999</v>
+        <v>3.1561</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4234</v>
+        <v>0.431</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0233</v>
+        <v>2.725</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1874</v>
+        <v>-2.0474</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9729</v>
+        <v>-1.2377</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2146</v>
+        <v>-0.8097</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6651</v>
+        <v>0.4403</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5346</v>
+        <v>0.4197</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1305</v>
+        <v>0.0206</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2186</v>
+        <v>-0.1895</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>-0.1895</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1189</v>
+        <v>1.4256</v>
       </c>
       <c r="E18" t="n">
-        <v>0.312</v>
+        <v>3.1392</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4309</v>
+        <v>-1.7137</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6159</v>
+        <v>2.6425</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.441</v>
+        <v>-1.7012</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1749</v>
+        <v>4.3437</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0219</v>
+        <v>5.993</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6127</v>
+        <v>0.165</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6346000000000001</v>
+        <v>5.8281</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6379</v>
+        <v>-3.3506</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8283</v>
+        <v>-1.8662</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8095</v>
+        <v>-1.4844</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.586</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>2.5395</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1417</v>
+        <v>0.1176</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0482</v>
+        <v>-0.1656</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0935</v>
+        <v>0.2832</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>0.0329</v>
       </c>
       <c r="W18" t="n">
         <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-1.1857</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4302</v>
+        <v>1.1008</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.615</v>
+        <v>3.595</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1848</v>
+        <v>-2.4942</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.294</v>
+        <v>-0.5876</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.957</v>
+        <v>-1.3963</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.337</v>
+        <v>0.8087</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4705</v>
+        <v>1.5999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0013</v>
+        <v>-0.4234</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4718</v>
+        <v>2.0233</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8235</v>
+        <v>-2.1874</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9583</v>
+        <v>-0.9729</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1348</v>
+        <v>-1.2146</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1362</v>
+        <v>0.6651</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1678</v>
+        <v>0.5346</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0316</v>
+        <v>0.1305</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA DISPES</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6628</v>
+        <v>-1.1189</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9559</v>
+        <v>0.312</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6187</v>
+        <v>-1.4309</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6871</v>
+        <v>-1.6159</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0269</v>
+        <v>-1.441</v>
       </c>
       <c r="I20" t="n">
-        <v>1.714</v>
+        <v>-0.1749</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8741</v>
+        <v>0.0219</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3505</v>
+        <v>-0.6127</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5237</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.187</v>
+        <v>-1.6379</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3773</v>
+        <v>-0.8283</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8097</v>
+        <v>-0.8095</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>0.478</v>
+        <v>0.1417</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0352</v>
+        <v>0.0482</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4429</v>
+        <v>0.0935</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4373</v>
+        <v>0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1762</v>
+        <v>-1.4302</v>
       </c>
       <c r="E21" t="n">
-        <v>0.114</v>
+        <v>-1.615</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2902</v>
+        <v>0.1848</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4417</v>
+        <v>-1.294</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4145</v>
+        <v>-0.957</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0272</v>
+        <v>-0.337</v>
       </c>
       <c r="J21" t="n">
-        <v>1.015</v>
+        <v>-0.4705</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0371</v>
+        <v>0.0013</v>
       </c>
       <c r="L21" t="n">
-        <v>1.0521</v>
+        <v>-0.4718</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.4567</v>
+        <v>-0.8235</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3773</v>
+        <v>-0.9583</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0793</v>
+        <v>0.1348</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>0.443</v>
+        <v>-0.1362</v>
       </c>
       <c r="T21" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.1678</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3672</v>
+        <v>0.0316</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.3495</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3495</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>R. GUARDIOLA DISPES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6548</v>
+        <v>-1.6628</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0005</v>
+        <v>0.9559</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6553</v>
+        <v>-2.6187</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8309</v>
+        <v>0.6871</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1159</v>
+        <v>-1.0269</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.715</v>
+        <v>1.714</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7151</v>
+        <v>2.8741</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2711</v>
+        <v>0.3505</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4439</v>
+        <v>2.5237</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.5459</v>
+        <v>-2.187</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.387</v>
+        <v>-1.3773</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.1589</v>
+        <v>-0.8097</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1025</v>
+        <v>0.478</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.112</v>
+        <v>0.0352</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0095</v>
+        <v>0.4429</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2553</v>
+        <v>-2.4373</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3276</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.0723</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2848</v>
+        <v>-2.1762</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0269</v>
+        <v>0.114</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.2579</v>
+        <v>-2.2902</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4284</v>
+        <v>-1.4417</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1612</v>
+        <v>-1.4145</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5896</v>
+        <v>-0.0272</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0412</v>
+        <v>1.015</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0642</v>
+        <v>-0.0371</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1054</v>
+        <v>1.0521</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3872</v>
+        <v>-2.4567</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.903</v>
+        <v>-1.3773</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4842</v>
+        <v>-1.0793</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0833</v>
+        <v>0.443</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2276</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1443</v>
+        <v>0.3672</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7731</v>
+        <v>-2.3495</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.9917</v>
+        <v>-2.3495</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-2.6548</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.0005</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-3.6553</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.8309</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.1159</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.715</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.7151</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.4439</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-3.5459</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.387</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-2.1589</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.1025</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.112</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.2553</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.3276</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.0723</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>M. SERRAT PONCE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.2848</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.0269</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-4.2579</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.4284</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1612</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.5896</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.0412</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.0642</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.1054</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.3872</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.903</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.4842</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.0833</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.1443</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.7731</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-2.9917</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484309_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-1.8475</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>17.4767</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>-19.3243</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>0.5828999999999986</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H26" t="n">
         <v>-8.860399999999998</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I26" t="n">
         <v>9.443300000000001</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J26" t="n">
         <v>21.7559</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K26" t="n">
         <v>2.1923</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>19.5637</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>-21.173</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>-11.0525</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O26" t="n">
         <v>-10.1204</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>-0.9766000000000001</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-14.6506</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>13.674</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>1.6508</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>0.455</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>1.1958</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>-3.104499999999999</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>9.916600000000001</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-13.021</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
